--- a/260711.xlsx
+++ b/260711.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tac3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73568992-8080-4313-BB62-82685DDBFE5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C57EBBE8-D02B-4581-A5D3-7F4A647DB15F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2620" yWindow="2620" windowWidth="16150" windowHeight="11170" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10470" yWindow="2250" windowWidth="15030" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Also muss man diese Selbstverständlichkeit in Erinnerung rufen.
 Wir wollen zurück zu dieser Kraftquelle.
@@ -45,13 +45,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>und aber auch Ideen anderer mit einzubringen.
-Hahne: Mit Chinas größtem 
-hat Ford zuletzt in den Sensorhersteller Velodyne
-auf einem Level four, wie es so schön heißt, auf der vierten Stufe von autonom fahrenden Fahrzeugen, wo ein Fahrer nicht mehr notwendigerweise eingreifen muss, wo es kein Lenkrad geben muss, wo es kein Gaspedal, kein Bremspedal gibt, das Fahrzeug fährt autonom</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>und Rechtsauffassungen des Bundesgerichtshofs erwirkt,  feste Strukturen aufweisen, so, wie es auch die bisherige, alte Rechtsprechung war.
 Und wenn sich aus Deutschland jemand in das syrische-irakische Kriegsgebiet begibt, dann ist das eine mitgliedschaftliche Betätigung.
 Und hierfür haben wir eine Reihe von Verurteilungen erwirkt.
@@ -70,6 +63,21 @@
 glaube ich, berücksichtigen müssen.
 Es geht eben immer auch um ganz grundsätzliche Demokratiefragen bei diesem Thema."</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>auch Ideen</t>
+  </si>
+  <si>
+    <t>wie es so schön heißt</t>
+  </si>
+  <si>
+    <t>Erinnerung rufen</t>
+  </si>
+  <si>
+    <t>vier, fünf Jahre her</t>
+  </si>
+  <si>
+    <t>recht erinnere</t>
   </si>
 </sst>
 </file>
@@ -403,15 +411,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFF013D0-15FD-4230-B377-278FFE076B7D}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="252" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -449,7 +477,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="308" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -468,7 +496,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="280" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
